--- a/output/第10期計画_事業所ヒアリングを行わない場合の外部資料による確認.xlsx
+++ b/output/第10期計画_事業所ヒアリングを行わない場合の外部資料による確認.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>令和8年10月21日</t>
+          <t>令和8年10月23日</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_事業所ヒアリングを行わない場合の外部資料による確認.xlsx
+++ b/output/第10期計画_事業所ヒアリングを行わない場合の外部資料による確認.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>令和8年10月23日</t>
+          <t>令和8年10月24日</t>
         </is>
       </c>
     </row>
